--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.1923603116776</v>
+        <v>9.456258550647609</v>
       </c>
       <c r="D2" t="n">
-        <v>57.6788001887325</v>
+        <v>9.372805030669031</v>
       </c>
       <c r="E2" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F2" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.64711494188479</v>
+        <v>6.930156178056278</v>
       </c>
       <c r="D3" t="n">
-        <v>42.37094274913716</v>
+        <v>6.885278196734788</v>
       </c>
       <c r="E3" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F3" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.62716520153577</v>
+        <v>11.31441434524956</v>
       </c>
       <c r="D4" t="n">
-        <v>69.10282613912335</v>
+        <v>11.22920924760754</v>
       </c>
       <c r="E4" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F4" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.78327323919832</v>
+        <v>8.414781901369727</v>
       </c>
       <c r="D5" t="n">
-        <v>51.24215441342876</v>
+        <v>8.326850092182173</v>
       </c>
       <c r="E5" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F5" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.48135951426388</v>
+        <v>5.11572092106788</v>
       </c>
       <c r="D6" t="n">
-        <v>30.99799985927699</v>
+        <v>5.037174977132512</v>
       </c>
       <c r="E6" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F6" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>66.63069904730851</v>
+        <v>10.82748859518763</v>
       </c>
       <c r="D7" t="n">
-        <v>66.15843915985742</v>
+        <v>10.75074636347683</v>
       </c>
       <c r="E7" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F7" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.23693506890085</v>
+        <v>10.60100194869639</v>
       </c>
       <c r="D8" t="n">
-        <v>63.10674924758536</v>
+        <v>10.25484675273262</v>
       </c>
       <c r="E8" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F8" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.46020985443472</v>
+        <v>9.824784101345642</v>
       </c>
       <c r="D9" t="n">
-        <v>60.76819306856662</v>
+        <v>9.874831373642076</v>
       </c>
       <c r="E9" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F9" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>67.70558135720745</v>
+        <v>11.00215697054621</v>
       </c>
       <c r="D10" t="n">
-        <v>68.03668529450314</v>
+        <v>11.05596136035676</v>
       </c>
       <c r="E10" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F10" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>68.39004835374442</v>
+        <v>11.11338285748347</v>
       </c>
       <c r="D11" t="n">
-        <v>68.7715904442119</v>
+        <v>11.17538344718443</v>
       </c>
       <c r="E11" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F11" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.10884483855396</v>
+        <v>5.217687286265019</v>
       </c>
       <c r="D12" t="n">
-        <v>32.59219045812718</v>
+        <v>5.296230949445667</v>
       </c>
       <c r="E12" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F12" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.93294768088055</v>
+        <v>4.864103998143089</v>
       </c>
       <c r="D13" t="n">
-        <v>29.78548688608044</v>
+        <v>4.840141618988071</v>
       </c>
       <c r="E13" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F13" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.6751181408705</v>
+        <v>5.147206697891456</v>
       </c>
       <c r="D14" t="n">
-        <v>29.61407767024847</v>
+        <v>4.812287621415377</v>
       </c>
       <c r="E14" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F14" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.04358757205381</v>
+        <v>4.882082980458744</v>
       </c>
       <c r="D15" t="n">
-        <v>30.57794259284883</v>
+        <v>4.968915671337935</v>
       </c>
       <c r="E15" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F15" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>61.92417478001136</v>
+        <v>10.06267840175185</v>
       </c>
       <c r="D16" t="n">
-        <v>62.4116703791881</v>
+        <v>10.14189643661807</v>
       </c>
       <c r="E16" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F16" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0211393493023</v>
+        <v>5.365935144261624</v>
       </c>
       <c r="D17" t="n">
-        <v>32.0978989285157</v>
+        <v>5.215908575883801</v>
       </c>
       <c r="E17" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F17" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>66.86532332631765</v>
+        <v>10.86561504052662</v>
       </c>
       <c r="D18" t="n">
-        <v>67.38116120721121</v>
+        <v>10.94943869617182</v>
       </c>
       <c r="E18" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F18" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>39.88759977152046</v>
+        <v>6.481734962872074</v>
       </c>
       <c r="D19" t="n">
-        <v>40.24447071037946</v>
+        <v>6.539726490436663</v>
       </c>
       <c r="E19" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F19" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>53.56680611037336</v>
+        <v>8.70460599293567</v>
       </c>
       <c r="D20" t="n">
-        <v>54.10693524843153</v>
+        <v>8.792376977870125</v>
       </c>
       <c r="E20" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F20" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>48.90704235110725</v>
+        <v>7.947394382054928</v>
       </c>
       <c r="D21" t="n">
-        <v>49.14686402527528</v>
+        <v>7.986365404107234</v>
       </c>
       <c r="E21" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F21" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>16.66392905990648</v>
+        <v>2.707888472234804</v>
       </c>
       <c r="D22" t="n">
-        <v>16.71127813325123</v>
+        <v>2.715582696653325</v>
       </c>
       <c r="E22" t="n">
-        <v>16.17735980050387</v>
+        <v>2.628820967581878</v>
       </c>
       <c r="F22" t="n">
-        <v>16.23968913429133</v>
+        <v>2.638949484322341</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
